--- a/report-2026-06-29.xlsx
+++ b/report-2026-06-29.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-29T09:57:06+05:30</t>
+    <t>Generated 2026-06-29T10:02:27+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T09:55:00+05:30 (2m5s ago)</t>
+    <t>2026-06-29T10:00:27+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -468,10 +468,16 @@
     <t>09:55:00.470</t>
   </si>
   <si>
+    <t>2026-06-29T10:00:07.5846976+05:30</t>
+  </si>
+  <si>
+    <t>10:00:07.584</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-29T09:57:06+05:30</t>
+    <t>2026-06-29T10:02:27+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1066,7 +1072,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 26s</t>
+          <t>0h 7m 47s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1086,7 +1092,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>81h 59m 24s</t>
+          <t>82h 0m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1096,7 +1102,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:57:06</t>
+          <t>10:02:27</t>
         </is>
       </c>
     </row>
@@ -1153,17 +1159,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>542.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>177157.2</t>
+          <t>98385.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1173,7 +1179,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>347</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1193,7 +1199,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>81h 58m 59s</t>
+          <t>82h 0m 14s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1203,7 +1209,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:57:06</t>
+          <t>10:02:27</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1328,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29T09:55:00.4705707+05:30</t>
+          <t>2026-06-29T10:00:07.5846976+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1332,7 +1338,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:55:00.470</t>
+          <t>10:00:07.584</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3615,18 +3621,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="s">
+    <row r="67">
+      <c r="A67" s="4">
+        <v>50</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C67" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
         <v>152</v>
       </c>
-      <c r="E68">
-        <v>49</v>
+      <c r="B69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-29.xlsx
+++ b/report-2026-06-29.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-29T10:02:27+05:30</t>
+    <t>Generated 2026-06-29T10:07:20+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:00:27+05:30 (2m0s ago)</t>
+    <t>2026-06-29T10:05:38+05:30 (1m41s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -474,10 +474,16 @@
     <t>10:00:07.584</t>
   </si>
   <si>
+    <t>2026-06-29T10:05:08.9751036+05:30</t>
+  </si>
+  <si>
+    <t>10:05:08.975</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-29T10:02:27+05:30</t>
+    <t>2026-06-29T10:07:20+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1072,7 +1078,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 47s</t>
+          <t>0h 12m 40s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1092,7 +1098,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>82h 0m 29s</t>
+          <t>82h 4m 4s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1102,7 +1108,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:02:27</t>
+          <t>10:07:20</t>
         </is>
       </c>
     </row>
@@ -1159,17 +1165,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>542.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>98385.6</t>
+          <t>148646.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1179,7 +1185,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>659</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1199,7 +1205,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>82h 0m 14s</t>
+          <t>82h 3m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1209,7 +1215,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:02:27</t>
+          <t>10:07:20</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1334,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29T10:00:07.5846976+05:30</t>
+          <t>2026-06-29T10:05:08.9751036+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1338,7 +1344,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:00:07.584</t>
+          <t>10:05:08.975</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3659,18 +3665,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="s">
+    <row r="68">
+      <c r="A68" s="4">
+        <v>51</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C68" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E68" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
         <v>154</v>
       </c>
-      <c r="E69">
-        <v>50</v>
+      <c r="B70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-29.xlsx
+++ b/report-2026-06-29.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-29T10:07:20+05:30</t>
+    <t>Generated 2026-06-29T10:07:38+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:05:38+05:30 (1m41s ago)</t>
+    <t>2026-06-29T10:05:38+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -483,7 +483,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-29T10:07:20+05:30</t>
+    <t>2026-06-29T10:07:38+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 40s</t>
+          <t>0h 12m 59s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:07:20</t>
+          <t>10:07:38</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>148646.8</t>
+          <t>178471.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:07:20</t>
+          <t>10:07:38</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-29.xlsx
+++ b/report-2026-06-29.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-29T10:07:38+05:30</t>
+    <t>Generated 2026-06-29T10:12:25+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:05:38+05:30 (2m0s ago)</t>
+    <t>2026-06-29T10:10:40+05:30 (1m44s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -480,10 +480,16 @@
     <t>10:05:08.975</t>
   </si>
   <si>
+    <t>2026-06-29T10:10:07.5828982+05:30</t>
+  </si>
+  <si>
+    <t>10:10:07.582</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-29T10:07:38+05:30</t>
+    <t>2026-06-29T10:12:25+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1043,7 +1049,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>server+agent</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1078,7 +1084,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 59s</t>
+          <t>0h 17m 45s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1098,7 +1104,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>82h 4m 4s</t>
+          <t>82h 4m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1108,7 +1114,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:07:38</t>
+          <t>10:12:25</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1146,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1150,42 +1156,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>178471.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1195,17 +1201,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 26 09:32 AM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:54:39</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>82h 3m 39s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1215,7 +1221,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:07:38</t>
+          <t>10:12:25</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1340,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29T10:05:08.9751036+05:30</t>
+          <t>2026-06-29T10:10:07.5828982+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1344,7 +1350,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:05:08.975</t>
+          <t>10:10:07.582</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3703,18 +3709,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="s">
+    <row r="69">
+      <c r="A69" s="4">
+        <v>52</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C69" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
         <v>156</v>
       </c>
-      <c r="E70">
-        <v>51</v>
+      <c r="B71" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
